--- a/uat-test-plans-reduced30/G2-16480-shipping-options-new-provider.xlsx
+++ b/uat-test-plans-reduced30/G2-16480-shipping-options-new-provider.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 7 UI-testable stories mapped to 10 business checks and 10 coverage rows. 14 backend-only/spike/setup stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 7 UI-testable stories mapped to 10 business checks and 10 coverage rows. 14 backend-only/spike/setup stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=13271; payload_chars=13269; est_tokens~3318; checklist_rows=7; matrix_rows=9; exploratory_rows=4</t>
+          <t>payload_bytes=13778; payload_chars=13776; est_tokens~3444; checklist_rows=7; matrix_rows=10; exploratory_rows=4</t>
         </is>
       </c>
     </row>
@@ -911,10 +911,10 @@
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
     </row>
-    <row r="6" ht="64" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-006</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -924,23 +924,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Cart State Lifecycle</t>
+          <t>Validation and Error Handling</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Porter empty-cart flow does not fail before first item is added</t>
+          <t>Invalid shipment or method inputs surface safe, user-facing errors</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Create or use an empty cart, set address, then add first item and continue shipping flow.</t>
+          <t>Exercise invalid shipmentId/method/cart combinations via UI path and verify visible feedback while checkout stays stable.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>No blocker occurs while cart has no shipment yet.
-Shipment-related flow initializes correctly after first item is added.</t>
+          <t>Errors are handled without breaking checkout.
+Messages are consistent and do not expose internal details.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -949,7 +949,7 @@
     <row r="7" ht="49" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -959,23 +959,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Validation and Error Handling</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Invalid shipment or method inputs surface safe, user-facing errors</t>
+          <t>Shipping option access respects cart ownership and user context</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Exercise invalid shipmentId/method/cart combinations via UI path and verify visible feedback while checkout stays stable.</t>
+          <t>Run guest and logged-in paths and validate that cart access from another user context is not exploitable.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Errors are handled without breaking checkout.
-Messages are consistent and do not expose internal details.</t>
+          <t>Authorized user/guest flows work.
+Cross-user access does not expose or mutate protected cart data.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -984,7 +984,7 @@
     <row r="8" ht="49" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-008</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -994,23 +994,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Cross-Brand Compatibility</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Shipping option access respects cart ownership and user context</t>
+          <t>Porter and mytheresa-compatible behaviors coexist without regression</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Run guest and logged-in paths and validate that cart access from another user context is not exploitable.</t>
+          <t>Execute core shipping-option checks on both target storefronts and compare expected behavior deltas.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Authorized user/guest flows work.
-Cross-user access does not expose or mutate protected cart data.</t>
+          <t>Brand-specific behavior is respected.
+No regression blocks the existing mytheresa-like flow.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1100,253 +1100,253 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>COV-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>G2-17592</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AC-G2-17592-FF</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Brand-dependent multiple shipment toggle and transparent behavior switch</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>GitHub commits found via MCP for G2-17592 in tapir and tapir-deployment</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Story AC is technical; business validation inferred through cross-brand behavior checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="49" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>COV-002</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>G2-20488</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>AC-G2-20488-SEL</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Shipment-level method selection endpoint behavior</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>UAT-002, UAT-006, UAT-007</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>GitHub commit evidence found; Jira QA comment confirms EXPRESS/STANDARD and guest/logged-in tests</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Acceptance text references API-level tests; mapped to business-level outcomes.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>COV-003</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>G2-20492</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>AC-G2-20492-EMPTYCART</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>No default shipment/method on porter empty cart with safe lifecycle</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>UAT-005</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>GitHub commit evidence found for default shipment logic removal</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Detailed technical AC requires business interpretation of expected UX transitions.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>COV-004</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>G2-20496</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>AC-G2-20496-FETCH</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Retrieve available methods through new porter-oriented endpoint</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>UAT-001, UAT-004, UAT-006</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>GitHub lookup attempt failed due secondary rate limit; Jira fallback scan found no explicit PR/commit URL</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Unavailable</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Jira comment indicates cross-user cart returns 200 empty list; potential policy ambiguity versus stricter forbidden response expectations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="49" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>COV-005</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>G2-20657</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>AC-G2-20657-MUT</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>GraphQL mutation for selecting shipment shipping method</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>UAT-002, UAT-006, UAT-007</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>GitHub lookup attempt failed due secondary rate limit; Jira fallback scan found no explicit PR/commit URL</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Mutation acceptance is API-centric; UAT maps to observable checkout effects.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>COV-006</t>
+          <t>COV-005</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>G2-20660</t>
+          <t>G2-20657</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-20660-QUERY</t>
+          <t>AC-G2-20657-MUT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>GraphQL query for shipment shipping methods retrieval</t>
+          <t>GraphQL mutation for selecting shipment shipping method</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-006, UAT-007</t>
+          <t>UAT-002, UAT-006, UAT-007</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1381,233 +1381,290 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Stolen cart behavior accepted as 200 empty list in Jira notes; monitor as potential authorization semantics gap.</t>
+          <t>Mutation acceptance is API-centric; UAT maps to observable checkout effects.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>COV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>G2-20660</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AC-G2-20660-QUERY</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>GraphQL query for shipment shipping methods retrieval</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>UAT-001, UAT-006, UAT-007</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>GitHub lookup attempt failed due secondary rate limit; Jira fallback scan found no explicit PR/commit URL</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Stolen cart behavior accepted as 200 empty list in Jira notes; monitor as potential authorization semantics gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="49" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>COV-007</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>G2-21737</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>AC-G2-21737-FE</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Display and selection UX for NAP and MRP shipping options</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>UAT-001, UAT-002, UAT-004</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Confluence scenario page retrieved (ID 186978245); GitHub lookup attempt rate-limited; Jira fallback had no PR/commit URL</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Unavailable</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Story itself is a spike-style statement; scenario details sourced from Confluence clarification page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>COV-008</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>G2-16480</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>AC-EPIC-001</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Customers can see and choose shipping options based on location and timing</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>UAT-001, UAT-002</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Epic AC plus story-level synthesis; Confluence Shipping Options page used for context</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Country matrix still marked as not fully confirmed in Confluence context page.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>COV-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>G2-16480</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>AC-EPIC-001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Customers can see and choose shipping options based on location and timing</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-001, UAT-002</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Epic AC plus story-level synthesis; Confluence Shipping Options page used for context</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Country matrix still marked as not fully confirmed in Confluence context page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>COV-009</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>G2-16480</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>AC-EPIC-002</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Option cost and conditions are visible and understandable</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>UAT-001</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Epic AC and FE scenario clarifications from Confluence</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Usability</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Exact wording and placement may vary by design scenario and shipment type.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="49" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="49" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>COV-010</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>G2-16480</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>AC-EPIC-003</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Default option handling when customer skips manual selection</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>UAT-003, UAT-004</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Epic AC plus backend lifecycle stories G2-20492 and G2-20496</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Default behavior differs by shipment scenario and brand rules; validate scenario coverage explicitly.</t>
         </is>

--- a/uat-test-plans-reduced30/G2-16480-shipping-options-new-provider.xlsx
+++ b/uat-test-plans-reduced30/G2-16480-shipping-options-new-provider.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 7 UI-testable stories mapped to 10 business checks and 10 coverage rows. 14 backend-only/spike/setup stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC coverage guardrail enforced] 7 UI-testable stories mapped to 10 business checks and 10 coverage rows. 14 backend-only/spike/setup stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=13778; payload_chars=13776; est_tokens~3444; checklist_rows=7; matrix_rows=10; exploratory_rows=4</t>
+          <t>payload_bytes=13763; payload_chars=13761; est_tokens~3441; checklist_rows=7; matrix_rows=10; exploratory_rows=4</t>
         </is>
       </c>
     </row>
